--- a/templates_formats/Lista_Seccion.xlsx
+++ b/templates_formats/Lista_Seccion.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>periodo escolar:</t>
   </si>
@@ -52,6 +52,9 @@
   </si>
   <si>
     <t>"NOMBRE MUNICIPIO","NOMBRE ESTADO"</t>
+  </si>
+  <si>
+    <t>LISTADO DE LA SECCION</t>
   </si>
 </sst>
 </file>
@@ -123,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
@@ -131,15 +134,6 @@
       <alignment horizontal="left" indent="4"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="6"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="12"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="13"/>
     </xf>
@@ -156,16 +150,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="23"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="18"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="19"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,13 +459,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:L69"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.875" customWidth="1"/>
+    <col min="1" max="1" width="14.375" customWidth="1"/>
     <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
-    <col min="4" max="4" width="49.875" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="58.75" customWidth="1"/>
     <col min="5" max="5" width="12.125" customWidth="1"/>
     <col min="6" max="6" width="12.625" customWidth="1"/>
     <col min="7" max="7" width="3.875" customWidth="1"/>
@@ -484,67 +475,86 @@
     <col min="13" max="13" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C1" s="14" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="13"/>
-    </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C2" s="15" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="13" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="5"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="7" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C5" s="16" t="s">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="3"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="D6" s="7" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C6" s="10" t="s">
         <v>0</v>
       </c>
+      <c r="D6" s="10"/>
       <c r="E6" s="3"/>
       <c r="G6" s="2"/>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="3"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="8" t="s">
+        <v>1</v>
+      </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="3"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -552,23 +562,22 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -577,84 +586,88 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
-        <v>1</v>
-      </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
-        <v>2</v>
-      </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>3</v>
-      </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
+        <v>2</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>4</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="6">
+        <v>3</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="9">
-        <v>5</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="6">
+        <v>4</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="9">
-        <v>6</v>
-      </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="6">
+        <v>5</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -662,13 +675,13 @@
       <c r="K16" s="2"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="9">
-        <v>7</v>
-      </c>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="B17" s="6">
+        <v>6</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -676,13 +689,13 @@
       <c r="K17" s="2"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="9">
-        <v>8</v>
-      </c>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="B18" s="6">
+        <v>7</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -690,13 +703,13 @@
       <c r="K18" s="2"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="9">
-        <v>9</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
+      <c r="B19" s="6">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -704,13 +717,13 @@
       <c r="K19" s="2"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="9">
-        <v>10</v>
-      </c>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="B20" s="6">
+        <v>9</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -718,13 +731,13 @@
       <c r="K20" s="2"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="9">
-        <v>11</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
+      <c r="B21" s="6">
+        <v>10</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -732,13 +745,13 @@
       <c r="K21" s="2"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="9">
-        <v>12</v>
-      </c>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
+      <c r="B22" s="6">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -746,13 +759,13 @@
       <c r="K22" s="2"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="9">
-        <v>13</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="B23" s="6">
+        <v>12</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -760,13 +773,13 @@
       <c r="K23" s="2"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="9">
-        <v>14</v>
-      </c>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="B24" s="6">
+        <v>13</v>
+      </c>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -774,13 +787,13 @@
       <c r="K24" s="2"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="9">
-        <v>15</v>
-      </c>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="B25" s="6">
+        <v>14</v>
+      </c>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -788,13 +801,13 @@
       <c r="K25" s="2"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="9">
-        <v>16</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="B26" s="6">
+        <v>15</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -802,13 +815,13 @@
       <c r="K26" s="2"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="9">
-        <v>17</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="B27" s="6">
+        <v>16</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
@@ -816,13 +829,13 @@
       <c r="K27" s="2"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="9">
-        <v>18</v>
-      </c>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
+      <c r="B28" s="6">
+        <v>17</v>
+      </c>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
@@ -830,13 +843,13 @@
       <c r="K28" s="2"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="9">
-        <v>19</v>
-      </c>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+      <c r="B29" s="6">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -844,13 +857,13 @@
       <c r="K29" s="2"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="9">
-        <v>20</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
+      <c r="B30" s="6">
+        <v>19</v>
+      </c>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
@@ -858,13 +871,13 @@
       <c r="K30" s="2"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="9">
-        <v>21</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="B31" s="6">
+        <v>20</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
@@ -872,460 +885,207 @@
       <c r="K31" s="2"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="9">
-        <v>22</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
+      <c r="B32" s="6">
+        <v>21</v>
+      </c>
+      <c r="C32" s="6"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="9">
-        <v>23</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="6">
+        <v>22</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B34" s="9">
-        <v>24</v>
-      </c>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="6">
+        <v>23</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="9">
-        <v>25</v>
-      </c>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="9">
-        <v>26</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="9">
-        <v>27</v>
-      </c>
-      <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="9">
-        <v>28</v>
-      </c>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
       <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="9">
-        <v>29</v>
-      </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="9">
-        <v>30</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="9">
-        <v>31</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
       <c r="I41" s="2"/>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="9">
-        <v>32</v>
-      </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B43" s="9">
-        <v>33</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="9">
-        <v>34</v>
-      </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="9">
-        <v>35</v>
-      </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="9">
-        <v>36</v>
-      </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="9">
-        <v>37</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="9">
-        <v>38</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
-      <c r="E55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
-      <c r="E57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2"/>
-    </row>
-    <row r="58" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-    </row>
-    <row r="59" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-    </row>
-    <row r="60" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
-      <c r="E60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2"/>
-    </row>
-    <row r="61" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2"/>
-    </row>
-    <row r="62" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="2"/>
-      <c r="K62" s="2"/>
-    </row>
-    <row r="63" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="2"/>
-      <c r="F63" s="2"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-    </row>
-    <row r="64" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="2"/>
-      <c r="K64" s="2"/>
-    </row>
-    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-    </row>
-    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C66" s="2"/>
-      <c r="D66" s="2"/>
-      <c r="E66" s="2"/>
-      <c r="F66" s="2"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="2"/>
-      <c r="K66" s="2"/>
-      <c r="L66" s="2"/>
-    </row>
-    <row r="67" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="2"/>
-      <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C68" s="2"/>
-      <c r="D68" s="2"/>
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="F69" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="172" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
+  <pageSetup paperSize="172" orientation="landscape" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
 </worksheet>
 </file>
 
